--- a/database/event/4236/event_4236_evp_summary.xlsx
+++ b/database/event/4236/event_4236_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.106999999999999</v>
+        <v>8.1972</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5068</v>
+        <v>2.5347</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8537</v>
+        <v>2.8219</v>
       </c>
       <c r="E2" t="n">
-        <v>8.106999999999999</v>
+        <v>8.1972</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4057</v>
+        <v>3.4959</v>
       </c>
       <c r="G2" t="n">
         <v>4.7013</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4057</v>
+        <v>3.4959</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4374</v>
+        <v>3.555</v>
       </c>
       <c r="J2" t="n">
         <v>4.7013</v>
@@ -529,7 +529,7 @@
         <v>319</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1387</v>
+        <v>8.2563</v>
       </c>
       <c r="N2" t="n">
         <v>543</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.2799</v>
+        <v>7.4086</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2511</v>
+        <v>2.2908</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5196</v>
+        <v>2.5077</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2799</v>
+        <v>7.4086</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3855</v>
+        <v>4.5142</v>
       </c>
       <c r="G3" t="n">
         <v>2.8944</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0832</v>
+        <v>5.6011</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1201</v>
+        <v>4.5399</v>
       </c>
       <c r="J3" t="n">
         <v>2.8944</v>
@@ -575,7 +575,7 @@
         <v>187</v>
       </c>
       <c r="M3" t="n">
-        <v>7.0145</v>
+        <v>7.4343</v>
       </c>
       <c r="N3" t="n">
         <v>311</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.2267</v>
+        <v>7.2278</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2346</v>
+        <v>2.2349</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4981</v>
+        <v>2.4356</v>
       </c>
       <c r="E4" t="n">
-        <v>7.2267</v>
+        <v>7.2278</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9711</v>
+        <v>2.9721</v>
       </c>
       <c r="G4" t="n">
         <v>4.2557</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9711</v>
+        <v>2.9721</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4081</v>
+        <v>2.409</v>
       </c>
       <c r="J4" t="n">
         <v>4.2557</v>
@@ -621,7 +621,7 @@
         <v>187</v>
       </c>
       <c r="M4" t="n">
-        <v>6.6638</v>
+        <v>6.6647</v>
       </c>
       <c r="N4" t="n">
         <v>311</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7503</v>
+        <v>6.7626</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0873</v>
+        <v>2.0911</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3056</v>
+        <v>2.2503</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7503</v>
+        <v>6.7626</v>
       </c>
       <c r="F5" t="n">
-        <v>4.525</v>
+        <v>4.5373</v>
       </c>
       <c r="G5" t="n">
         <v>2.2253</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6446</v>
+        <v>5.6943</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5751</v>
+        <v>4.6154</v>
       </c>
       <c r="J5" t="n">
         <v>2.2253</v>
@@ -667,7 +667,7 @@
         <v>187</v>
       </c>
       <c r="M5" t="n">
-        <v>6.8004</v>
+        <v>6.8407</v>
       </c>
       <c r="N5" t="n">
         <v>311</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.2221</v>
+        <v>6.6736</v>
       </c>
       <c r="C6" t="n">
-        <v>1.924</v>
+        <v>2.0636</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0922</v>
+        <v>2.2149</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2221</v>
+        <v>6.6736</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6451</v>
+        <v>3.0966</v>
       </c>
       <c r="G6" t="n">
         <v>3.577</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6451</v>
+        <v>3.0966</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6698</v>
+        <v>3.1489</v>
       </c>
       <c r="J6" t="n">
         <v>3.577</v>
@@ -713,7 +713,7 @@
         <v>319</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2468</v>
+        <v>6.725899999999999</v>
       </c>
       <c r="N6" t="n">
         <v>543</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.2475</v>
+        <v>5.3748</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6226</v>
+        <v>1.662</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6985</v>
+        <v>1.6974</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2475</v>
+        <v>5.3748</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3279</v>
+        <v>2.4553</v>
       </c>
       <c r="G7" t="n">
         <v>2.9196</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3279</v>
+        <v>2.4553</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3279</v>
+        <v>2.4553</v>
       </c>
       <c r="J7" t="n">
         <v>2.9196</v>
@@ -759,7 +759,7 @@
         <v>127</v>
       </c>
       <c r="M7" t="n">
-        <v>5.2475</v>
+        <v>5.3749</v>
       </c>
       <c r="N7" t="n">
         <v>246</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.8977</v>
+        <v>4.9566</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5144</v>
+        <v>1.5327</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5572</v>
+        <v>1.5308</v>
       </c>
       <c r="E8" t="n">
-        <v>4.8977</v>
+        <v>4.9566</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5057</v>
+        <v>4.5646</v>
       </c>
       <c r="G8" t="n">
         <v>0.392</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5671</v>
+        <v>5.8039</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5123</v>
+        <v>4.7042</v>
       </c>
       <c r="J8" t="n">
         <v>0.392</v>
@@ -805,7 +805,7 @@
         <v>77</v>
       </c>
       <c r="M8" t="n">
-        <v>4.9043</v>
+        <v>5.096200000000001</v>
       </c>
       <c r="N8" t="n">
         <v>199</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6548</v>
+        <v>4.6569</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4393</v>
+        <v>1.44</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4591</v>
+        <v>1.4114</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6548</v>
+        <v>4.6569</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5992</v>
+        <v>4.8526</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0556</v>
+        <v>-0.1957</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9086</v>
+        <v>6.9626</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9774</v>
+        <v>5.6434</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0556</v>
+        <v>-0.1957</v>
       </c>
       <c r="K9" t="n">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="L9" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>5.033</v>
+        <v>5.447699999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>226</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.5223</v>
+        <v>4.6199</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3984</v>
+        <v>1.4285</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4055</v>
+        <v>1.3967</v>
       </c>
       <c r="E10" t="n">
-        <v>4.5223</v>
+        <v>4.6199</v>
       </c>
       <c r="F10" t="n">
-        <v>4.718</v>
+        <v>4.5643</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1957</v>
+        <v>0.0556</v>
       </c>
       <c r="H10" t="n">
-        <v>6.421</v>
+        <v>4.8538</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2044</v>
+        <v>4.9774</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1957</v>
+        <v>0.0556</v>
       </c>
       <c r="K10" t="n">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="L10" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="M10" t="n">
-        <v>5.008699999999999</v>
+        <v>5.033</v>
       </c>
       <c r="N10" t="n">
-        <v>199</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -916,7 +916,7 @@
         <v>1.3785</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3796</v>
+        <v>1.3322</v>
       </c>
       <c r="E11" t="n">
         <v>4.4581</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.2796</v>
+        <v>4.2406</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3233</v>
+        <v>1.3113</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3075</v>
+        <v>1.2455</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2796</v>
+        <v>4.2406</v>
       </c>
       <c r="F12" t="n">
-        <v>4.9685</v>
+        <v>4.9295</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6889</v>
       </c>
       <c r="H12" t="n">
-        <v>5.4876</v>
+        <v>5.4264</v>
       </c>
       <c r="I12" t="n">
         <v>5.5646</v>
@@ -998,277 +998,277 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.9445</v>
+        <v>4.0332</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2197</v>
+        <v>1.2471</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1721</v>
+        <v>1.1629</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9445</v>
+        <v>4.0332</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7358</v>
+        <v>2.3376</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2087</v>
+        <v>1.6956</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7358</v>
+        <v>2.3376</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7882</v>
+        <v>2.3771</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2087</v>
+        <v>1.6956</v>
       </c>
       <c r="K13" t="n">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="L13" t="n">
-        <v>67</v>
+        <v>319</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9969</v>
+        <v>4.0727</v>
       </c>
       <c r="N13" t="n">
-        <v>226</v>
+        <v>543</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.8872</v>
+        <v>3.909</v>
       </c>
       <c r="C14" t="n">
-        <v>1.202</v>
+        <v>1.2087</v>
       </c>
       <c r="D14" t="n">
-        <v>1.149</v>
+        <v>1.1134</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8872</v>
+        <v>3.909</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7214</v>
+        <v>2.5858</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1658</v>
+        <v>1.3232</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7214</v>
+        <v>2.5858</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0163</v>
+        <v>2.5858</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1658</v>
+        <v>1.3232</v>
       </c>
       <c r="K14" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="L14" t="n">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1821</v>
+        <v>3.909</v>
       </c>
       <c r="N14" t="n">
-        <v>199</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.6797</v>
+        <v>3.9029</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1378</v>
+        <v>1.2068</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0652</v>
+        <v>1.111</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6797</v>
+        <v>3.9029</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9841</v>
+        <v>3.6942</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6956</v>
+        <v>0.2087</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9841</v>
+        <v>3.6942</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0026</v>
+        <v>3.7882</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6956</v>
+        <v>0.2087</v>
       </c>
       <c r="K15" t="n">
-        <v>224</v>
+        <v>159</v>
       </c>
       <c r="L15" t="n">
-        <v>319</v>
+        <v>67</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6982</v>
+        <v>3.9969</v>
       </c>
       <c r="N15" t="n">
-        <v>543</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.3349</v>
+        <v>3.8872</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0312</v>
+        <v>1.202</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9258999999999999</v>
+        <v>1.1048</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3349</v>
+        <v>3.8872</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0117</v>
+        <v>3.7214</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3232</v>
+        <v>0.1658</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0117</v>
+        <v>3.7214</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0117</v>
+        <v>3.0163</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3232</v>
+        <v>0.1658</v>
       </c>
       <c r="K16" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="L16" t="n">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3349</v>
+        <v>3.1821</v>
       </c>
       <c r="N16" t="n">
-        <v>249</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.2533</v>
+        <v>3.452</v>
       </c>
       <c r="C17" t="n">
-        <v>1.006</v>
+        <v>1.0674</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8929</v>
+        <v>0.9314</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2533</v>
+        <v>3.452</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2533</v>
+        <v>4.105</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.653</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2533</v>
+        <v>4.105</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2837</v>
+        <v>3.3272</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.653</v>
       </c>
       <c r="K17" t="n">
-        <v>276</v>
+        <v>124</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2837</v>
+        <v>2.6742</v>
       </c>
       <c r="N17" t="n">
-        <v>276</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.2036</v>
+        <v>3.2291</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9906</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8728</v>
+        <v>0.8426</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2036</v>
+        <v>3.2291</v>
       </c>
       <c r="F18" t="n">
-        <v>3.8566</v>
+        <v>3.2291</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.653</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8566</v>
+        <v>3.2291</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1258</v>
+        <v>3.2837</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.653</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>124</v>
+        <v>276</v>
       </c>
       <c r="L18" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.4728</v>
+        <v>3.2837</v>
       </c>
       <c r="N18" t="n">
-        <v>311</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.1884</v>
+        <v>3.1937</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9859</v>
+        <v>0.9875</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8667</v>
+        <v>0.8285</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1884</v>
+        <v>3.1937</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2018</v>
+        <v>2.2071</v>
       </c>
       <c r="G19" t="n">
         <v>0.9866</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2018</v>
+        <v>2.2071</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7846</v>
+        <v>1.7889</v>
       </c>
       <c r="J19" t="n">
         <v>0.9866</v>
@@ -1311,7 +1311,7 @@
         <v>187</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7712</v>
+        <v>2.7755</v>
       </c>
       <c r="N19" t="n">
         <v>311</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6016</v>
+        <v>2.578</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8045</v>
+        <v>0.7972</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6296</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6016</v>
+        <v>2.578</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1097</v>
+        <v>2.0861</v>
       </c>
       <c r="G20" t="n">
         <v>0.4919</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1097</v>
+        <v>2.0861</v>
       </c>
       <c r="I20" t="n">
         <v>2.1393</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5395</v>
+        <v>2.5048</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7853</v>
+        <v>0.7745</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6045</v>
+        <v>0.554</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5395</v>
+        <v>2.5048</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1084</v>
+        <v>3.0737</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5689</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1084</v>
+        <v>3.0737</v>
       </c>
       <c r="I21" t="n">
         <v>3.152</v>
@@ -1412,737 +1412,737 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.2247</v>
+        <v>2.2769</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6879</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4774</v>
+        <v>0.4632</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2247</v>
+        <v>2.2769</v>
       </c>
       <c r="F22" t="n">
-        <v>1.639</v>
+        <v>2.958</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5857</v>
+        <v>-0.6811</v>
       </c>
       <c r="H22" t="n">
-        <v>1.639</v>
+        <v>2.958</v>
       </c>
       <c r="I22" t="n">
-        <v>1.639</v>
+        <v>2.958</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5857</v>
+        <v>-0.6811</v>
       </c>
       <c r="K22" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="L22" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="M22" t="n">
-        <v>2.2247</v>
+        <v>2.2769</v>
       </c>
       <c r="N22" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1198</v>
+        <v>2.2247</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6555</v>
+        <v>0.6879</v>
       </c>
       <c r="D23" t="n">
-        <v>0.435</v>
+        <v>0.4424</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1198</v>
+        <v>2.2247</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8009</v>
+        <v>1.639</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6811</v>
+        <v>0.5857</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8009</v>
+        <v>1.639</v>
       </c>
       <c r="I23" t="n">
-        <v>2.8009</v>
+        <v>1.639</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6811</v>
+        <v>0.5857</v>
       </c>
       <c r="K23" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="L23" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="M23" t="n">
-        <v>2.1198</v>
+        <v>2.2247</v>
       </c>
       <c r="N23" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9736</v>
+        <v>2.1331</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6103</v>
+        <v>0.6596</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3759</v>
+        <v>0.4059</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9736</v>
+        <v>2.1331</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0696</v>
+        <v>2.1331</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.096</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.0696</v>
+        <v>2.1331</v>
       </c>
       <c r="I24" t="n">
-        <v>2.0889</v>
+        <v>2.1331</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.096</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>224</v>
+        <v>162</v>
       </c>
       <c r="L24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9929</v>
+        <v>2.1331</v>
       </c>
       <c r="N24" t="n">
-        <v>543</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.478</v>
+        <v>1.9581</v>
       </c>
       <c r="C25" t="n">
-        <v>0.457</v>
+        <v>0.6055</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1757</v>
+        <v>0.3362</v>
       </c>
       <c r="E25" t="n">
-        <v>1.478</v>
+        <v>1.9581</v>
       </c>
       <c r="F25" t="n">
-        <v>1.478</v>
+        <v>2.0541</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.096</v>
       </c>
       <c r="H25" t="n">
-        <v>1.478</v>
+        <v>2.0541</v>
       </c>
       <c r="I25" t="n">
-        <v>1.478</v>
+        <v>2.0889</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.096</v>
       </c>
       <c r="K25" t="n">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="M25" t="n">
-        <v>1.478</v>
+        <v>1.9929</v>
       </c>
       <c r="N25" t="n">
-        <v>162</v>
+        <v>543</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3703</v>
+        <v>1.7113</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4237</v>
+        <v>0.5292</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1322</v>
+        <v>0.2379</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3703</v>
+        <v>1.7113</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7075</v>
+        <v>1.7113</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3372</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7075</v>
+        <v>1.7113</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7075</v>
+        <v>1.7113</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3372</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="L26" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3703</v>
+        <v>1.7113</v>
       </c>
       <c r="N26" t="n">
-        <v>249</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3013</v>
+        <v>1.6786</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4024</v>
+        <v>0.519</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1043</v>
+        <v>0.2248</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3013</v>
+        <v>1.6786</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3013</v>
+        <v>1.6786</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3013</v>
+        <v>1.6786</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3013</v>
+        <v>1.6786</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3013</v>
+        <v>1.6786</v>
       </c>
       <c r="N27" t="n">
-        <v>178</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.2938</v>
+        <v>1.5212</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4001</v>
+        <v>0.4704</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1013</v>
+        <v>0.1621</v>
       </c>
       <c r="E28" t="n">
-        <v>1.2938</v>
+        <v>1.5212</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1767</v>
+        <v>1.8584</v>
       </c>
       <c r="G28" t="n">
-        <v>1.4705</v>
+        <v>-0.3372</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1767</v>
+        <v>1.8584</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1767</v>
+        <v>1.8584</v>
       </c>
       <c r="J28" t="n">
-        <v>1.4705</v>
+        <v>-0.3372</v>
       </c>
       <c r="K28" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="L28" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="M28" t="n">
-        <v>1.2938</v>
+        <v>1.5212</v>
       </c>
       <c r="N28" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sico</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2563</v>
+        <v>1.3684</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3885</v>
+        <v>0.4231</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0862</v>
+        <v>0.1013</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2563</v>
+        <v>1.3684</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2563</v>
+        <v>1.3684</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.2563</v>
+        <v>1.3684</v>
       </c>
       <c r="I29" t="n">
-        <v>1.268</v>
+        <v>1.3684</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>276</v>
+        <v>128</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.268</v>
+        <v>1.3684</v>
       </c>
       <c r="N29" t="n">
-        <v>276</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2171</v>
+        <v>1.3014</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3763</v>
+        <v>0.4024</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0703</v>
+        <v>0.0746</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2171</v>
+        <v>1.3014</v>
       </c>
       <c r="F30" t="n">
-        <v>1.2171</v>
+        <v>1.3014</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2171</v>
+        <v>1.3014</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2171</v>
+        <v>1.3014</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2171</v>
+        <v>1.3014</v>
       </c>
       <c r="N30" t="n">
-        <v>128</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1055</v>
+        <v>1.2938</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3418</v>
+        <v>0.4001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0252</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1055</v>
+        <v>1.2938</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1055</v>
+        <v>-0.1767</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.4705</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1055</v>
+        <v>-0.1767</v>
       </c>
       <c r="I31" t="n">
-        <v>1.1055</v>
+        <v>-0.1767</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.4705</v>
       </c>
       <c r="K31" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1055</v>
+        <v>1.2938</v>
       </c>
       <c r="N31" t="n">
-        <v>105</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Sico</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.0382</v>
+        <v>1.2469</v>
       </c>
       <c r="C32" t="n">
-        <v>0.321</v>
+        <v>0.3856</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.002</v>
+        <v>0.0529</v>
       </c>
       <c r="E32" t="n">
-        <v>1.0382</v>
+        <v>1.2469</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0382</v>
+        <v>1.2469</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0382</v>
+        <v>1.2469</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0382</v>
+        <v>1.268</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>97</v>
+        <v>276</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.0382</v>
+        <v>1.268</v>
       </c>
       <c r="N32" t="n">
-        <v>97</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9059</v>
+        <v>1.2369</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2801</v>
+        <v>0.3825</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0554</v>
+        <v>0.0489</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9059</v>
+        <v>1.2369</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9059</v>
+        <v>2.0235</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.7866</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9059</v>
+        <v>2.0235</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9059</v>
+        <v>2.0235</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.7866</v>
       </c>
       <c r="K33" t="n">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9059</v>
+        <v>1.2369</v>
       </c>
       <c r="N33" t="n">
-        <v>178</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>moose</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8918</v>
+        <v>1.1055</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2758</v>
+        <v>0.3418</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0611</v>
+        <v>-0.0035</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8918</v>
+        <v>1.1055</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8918</v>
+        <v>1.1055</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8918</v>
+        <v>1.1055</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8918</v>
+        <v>1.1055</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8918</v>
+        <v>1.1055</v>
       </c>
       <c r="N34" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8842</v>
+        <v>1.0382</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2734</v>
+        <v>0.321</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0303</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8842</v>
+        <v>1.0382</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8842</v>
+        <v>1.0382</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8842</v>
+        <v>1.0382</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8842</v>
+        <v>1.0382</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8842</v>
+        <v>1.0382</v>
       </c>
       <c r="N35" t="n">
-        <v>162</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>moose</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8555</v>
+        <v>0.8918</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2645</v>
+        <v>0.2758</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0886</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8555</v>
+        <v>0.8918</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8555</v>
+        <v>0.8918</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8555</v>
+        <v>0.8918</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8555</v>
+        <v>0.8918</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8555</v>
+        <v>0.8918</v>
       </c>
       <c r="N36" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8514</v>
+        <v>0.8842</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2633</v>
+        <v>0.2734</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0774</v>
+        <v>-0.0916</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8514</v>
+        <v>0.8842</v>
       </c>
       <c r="F37" t="n">
-        <v>1.638</v>
+        <v>0.8842</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7866</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.638</v>
+        <v>0.8842</v>
       </c>
       <c r="I37" t="n">
-        <v>1.638</v>
+        <v>0.8842</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7866</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="L37" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8513999999999999</v>
+        <v>0.8842</v>
       </c>
       <c r="N37" t="n">
-        <v>246</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38">
@@ -2158,7 +2158,7 @@
         <v>0.2115</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.145</v>
+        <v>-0.1714</v>
       </c>
       <c r="E38" t="n">
         <v>0.6841</v>
@@ -2204,7 +2204,7 @@
         <v>0.183</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1823</v>
+        <v>-0.2082</v>
       </c>
       <c r="E39" t="n">
         <v>0.5917</v>
@@ -2250,7 +2250,7 @@
         <v>0.158</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.215</v>
+        <v>-0.2404</v>
       </c>
       <c r="E40" t="n">
         <v>0.5109</v>
@@ -2296,7 +2296,7 @@
         <v>0.1467</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2297</v>
+        <v>-0.2549</v>
       </c>
       <c r="E41" t="n">
         <v>0.4745</v>
@@ -2342,7 +2342,7 @@
         <v>0.1387</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2402</v>
+        <v>-0.2652</v>
       </c>
       <c r="E42" t="n">
         <v>0.4485</v>
@@ -2388,7 +2388,7 @@
         <v>0.1361</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2435</v>
+        <v>-0.2685</v>
       </c>
       <c r="E43" t="n">
         <v>0.4402</v>
@@ -2434,7 +2434,7 @@
         <v>0.0891</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.305</v>
+        <v>-0.3291</v>
       </c>
       <c r="E44" t="n">
         <v>0.2881</v>
@@ -2480,7 +2480,7 @@
         <v>0.067</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3338</v>
+        <v>-0.3575</v>
       </c>
       <c r="E45" t="n">
         <v>0.2168</v>
@@ -2526,7 +2526,7 @@
         <v>0.0663</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3347</v>
+        <v>-0.3585</v>
       </c>
       <c r="E46" t="n">
         <v>0.2144</v>
@@ -2572,7 +2572,7 @@
         <v>0.0613</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3413</v>
+        <v>-0.3649</v>
       </c>
       <c r="E47" t="n">
         <v>0.1982</v>
@@ -2618,7 +2618,7 @@
         <v>0.052</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3534</v>
+        <v>-0.3769</v>
       </c>
       <c r="E48" t="n">
         <v>0.1682</v>
@@ -2654,93 +2654,93 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.138</v>
+        <v>0.1397</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0427</v>
+        <v>0.0432</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3656</v>
+        <v>-0.3883</v>
       </c>
       <c r="E49" t="n">
-        <v>0.138</v>
+        <v>0.1397</v>
       </c>
       <c r="F49" t="n">
-        <v>0.138</v>
+        <v>0.1397</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.138</v>
+        <v>0.1397</v>
       </c>
       <c r="I49" t="n">
-        <v>0.138</v>
+        <v>0.1397</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.138</v>
+        <v>0.1397</v>
       </c>
       <c r="N49" t="n">
-        <v>105</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.129</v>
+        <v>0.138</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0399</v>
+        <v>0.0427</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3692</v>
+        <v>-0.3889</v>
       </c>
       <c r="E50" t="n">
-        <v>0.129</v>
+        <v>0.138</v>
       </c>
       <c r="F50" t="n">
-        <v>0.129</v>
+        <v>0.138</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.129</v>
+        <v>0.138</v>
       </c>
       <c r="I50" t="n">
-        <v>0.129</v>
+        <v>0.138</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.129</v>
+        <v>0.138</v>
       </c>
       <c r="N50" t="n">
-        <v>162</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51">
@@ -2756,7 +2756,7 @@
         <v>0.0369</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3731</v>
+        <v>-0.3963</v>
       </c>
       <c r="E51" t="n">
         <v>0.1194</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1127</v>
+        <v>-0.1119</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0348</v>
+        <v>-0.0346</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4669</v>
+        <v>-0.4885</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1127</v>
+        <v>-0.1119</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1127</v>
+        <v>-0.1119</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1127</v>
+        <v>-0.1119</v>
       </c>
       <c r="I52" t="n">
         <v>-0.1138</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0466</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4822</v>
+        <v>-0.5039</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1506</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2091</v>
+        <v>-0.2076</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5058</v>
+        <v>-0.5266</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2091</v>
+        <v>-0.2076</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2091</v>
+        <v>-0.2076</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2091</v>
+        <v>-0.2076</v>
       </c>
       <c r="I54" t="n">
         <v>-0.2111</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0808</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5269</v>
+        <v>-0.548</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2613</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2796</v>
+        <v>-0.2759</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0853</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5343</v>
+        <v>-0.5538</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2796</v>
+        <v>-0.2759</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4967</v>
+        <v>-0.493</v>
       </c>
       <c r="G56" t="n">
         <v>0.2171</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4967</v>
+        <v>-0.493</v>
       </c>
       <c r="I56" t="n">
         <v>-0.5013</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1131</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5692</v>
+        <v>-0.5897</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3659</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1556</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6247</v>
+        <v>-0.6444</v>
       </c>
       <c r="E58" t="n">
         <v>-0.5033</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1588</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6288</v>
+        <v>-0.6485</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5135999999999999</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1632</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6542</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5278</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1694</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6427</v>
+        <v>-0.6622</v>
       </c>
       <c r="E61" t="n">
         <v>-0.5478</v>
@@ -3262,7 +3262,7 @@
         <v>-0.1803</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6569</v>
+        <v>-0.6762</v>
       </c>
       <c r="E62" t="n">
         <v>-0.583</v>
@@ -3308,7 +3308,7 @@
         <v>-0.3095</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8257</v>
+        <v>-0.8427</v>
       </c>
       <c r="E63" t="n">
         <v>-1.001</v>
@@ -3354,7 +3354,7 @@
         <v>-0.319</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8381</v>
+        <v>-0.8549</v>
       </c>
       <c r="E64" t="n">
         <v>-1.0316</v>
@@ -3400,7 +3400,7 @@
         <v>-0.33</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8525</v>
+        <v>-0.8691</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0672</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3522</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8815</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="E66" t="n">
         <v>-1.139</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3744</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9105</v>
+        <v>-0.9263</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2107</v>
@@ -3538,7 +3538,7 @@
         <v>-0.3783</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9156</v>
+        <v>-0.9314</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2235</v>
@@ -3584,7 +3584,7 @@
         <v>-0.4322</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.986</v>
+        <v>-1.0008</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3977</v>
@@ -3630,7 +3630,7 @@
         <v>-0.4331</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9872</v>
+        <v>-1.0019</v>
       </c>
       <c r="E70" t="n">
         <v>-1.4006</v>
@@ -3676,7 +3676,7 @@
         <v>-0.4782</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0461</v>
+        <v>-1.06</v>
       </c>
       <c r="E71" t="n">
         <v>-1.5464</v>
@@ -3722,7 +3722,7 @@
         <v>-0.4941</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0669</v>
+        <v>-1.0805</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5979</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5067</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0834</v>
+        <v>-1.0968</v>
       </c>
       <c r="E73" t="n">
         <v>-1.6388</v>
@@ -3814,7 +3814,7 @@
         <v>-0.517</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0968</v>
+        <v>-1.11</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6719</v>
@@ -3860,7 +3860,7 @@
         <v>-0.5212</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1023</v>
+        <v>-1.1155</v>
       </c>
       <c r="E75" t="n">
         <v>-1.6856</v>
@@ -3906,7 +3906,7 @@
         <v>-0.5349</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1202</v>
+        <v>-1.1331</v>
       </c>
       <c r="E76" t="n">
         <v>-1.7299</v>
@@ -3952,7 +3952,7 @@
         <v>-0.5462</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1349</v>
+        <v>-1.1476</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7663</v>
@@ -3998,7 +3998,7 @@
         <v>-0.5464</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1353</v>
+        <v>-1.148</v>
       </c>
       <c r="E78" t="n">
         <v>-1.7672</v>
@@ -4044,7 +4044,7 @@
         <v>-0.5957</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1996</v>
+        <v>-1.2114</v>
       </c>
       <c r="E79" t="n">
         <v>-1.9264</v>
@@ -4090,7 +4090,7 @@
         <v>-0.6056</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2125</v>
+        <v>-1.2241</v>
       </c>
       <c r="E80" t="n">
         <v>-1.9584</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.3279</v>
+        <v>-3.3032</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.029</v>
+        <v>-1.0214</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7658</v>
+        <v>-1.7599</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.3279</v>
+        <v>-3.3032</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.3279</v>
+        <v>-3.3032</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.3279</v>
+        <v>-3.3032</v>
       </c>
       <c r="I81" t="n">
         <v>-3.359</v>
@@ -4182,7 +4182,7 @@
         <v>-1.524</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.4124</v>
+        <v>-2.4075</v>
       </c>
       <c r="E82" t="n">
         <v>-4.9286</v>
